--- a/SGC-CKN/Excel/3cfb93bc-b746-45bb-98e2-62340827647b_PA-159_PA-159_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/3cfb93bc-b746-45bb-98e2-62340827647b_PA-159_PA-159_D800_25-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -33,6 +33,9 @@
   </si>
   <si>
     <t>Số hiệu cọc</t>
+  </si>
+  <si>
+    <t>P1-139</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -1012,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1026,10 +1029,10 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1043,10 +1046,10 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1060,10 +1063,10 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1077,10 +1080,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1095,57 +1098,57 @@
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.73</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.73</v>
@@ -1157,173 +1160,173 @@
         <v>1.73</v>
       </c>
       <c r="J11" s="8">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-1.73</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="H12" s="9">
         <v>0.58</v>
       </c>
       <c r="I12" s="9">
-        <v>8.12</v>
+        <v>3.12</v>
       </c>
       <c r="J12" s="12">
-        <v>13.92</v>
+        <v>5.35</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>32</v>
-      </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="G13" s="13">
-        <v>-18.55</v>
+        <v>-8.15</v>
       </c>
       <c r="H13" s="13">
         <v>0.58</v>
       </c>
       <c r="I13" s="13">
-        <v>8.7</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="12">
-        <v>14.91</v>
+        <v>5.66</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>35</v>
-      </c>
       <c r="E14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16">
-        <v>-18.55</v>
+        <v>-8.15</v>
       </c>
       <c r="G14" s="16">
-        <v>-21.95</v>
+        <v>-16.95</v>
       </c>
       <c r="H14" s="16">
         <v>1.33</v>
       </c>
       <c r="I14" s="16">
-        <v>3.4</v>
-      </c>
-      <c r="J14" s="8">
-        <v>2.55</v>
+        <v>8.8</v>
+      </c>
+      <c r="J14" s="12">
+        <v>6.6</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>38</v>
-      </c>
       <c r="E15" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="19">
-        <v>-21.95</v>
+        <v>-16.95</v>
       </c>
       <c r="G15" s="19">
-        <v>-26.15</v>
+        <v>-22.15</v>
       </c>
       <c r="H15" s="19">
         <v>2.58</v>
       </c>
       <c r="I15" s="19">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="J15" s="8">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>41</v>
-      </c>
       <c r="E16" s="24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="22">
+        <v>-22.15</v>
+      </c>
+      <c r="G16" s="22">
         <v>-26.15</v>
-      </c>
-      <c r="G16" s="22">
-        <v>-30.15</v>
       </c>
       <c r="H16" s="22">
         <v>0.83</v>
@@ -1335,62 +1338,62 @@
         <v>4.8</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>44</v>
-      </c>
       <c r="E17" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-30.15</v>
+        <v>-26.15</v>
       </c>
       <c r="G17" s="25">
-        <v>-36.47</v>
+        <v>-30.5</v>
       </c>
       <c r="H17" s="25">
         <v>1.5</v>
       </c>
       <c r="I17" s="25">
-        <v>6.32</v>
+        <v>4.35</v>
       </c>
       <c r="J17" s="8">
-        <v>4.21</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="28">
-        <v>-36.47</v>
+        <v>-30.5</v>
       </c>
       <c r="G18" s="28">
         <v>-44.25</v>
@@ -1399,18 +1402,18 @@
         <v>2.58</v>
       </c>
       <c r="I18" s="28">
-        <v>7.78</v>
-      </c>
-      <c r="J18" s="8">
-        <v>3.01</v>
+        <v>13.75</v>
+      </c>
+      <c r="J18" s="12">
+        <v>5.32</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1516,31 +1519,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1548,16 +1551,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.73</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.73</v>
@@ -1577,10 +1580,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1589,16 +1592,16 @@
         <v>-1.73</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="G3" s="9">
         <v>0.58</v>
       </c>
       <c r="H3" s="9">
-        <v>8.12</v>
+        <v>3.12</v>
       </c>
       <c r="I3" s="12">
-        <v>13.92</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,28 +1609,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-9.85</v>
+        <v>-4.85</v>
       </c>
       <c r="F4" s="13">
-        <v>-18.55</v>
+        <v>-8.15</v>
       </c>
       <c r="G4" s="13">
         <v>0.58</v>
       </c>
       <c r="H4" s="13">
-        <v>8.7</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="12">
-        <v>14.91</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1635,28 +1638,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-18.55</v>
+        <v>-8.15</v>
       </c>
       <c r="F5" s="16">
-        <v>-21.95</v>
+        <v>-16.95</v>
       </c>
       <c r="G5" s="16">
         <v>1.33</v>
       </c>
       <c r="H5" s="16">
-        <v>3.4</v>
-      </c>
-      <c r="I5" s="8">
-        <v>2.55</v>
+        <v>8.8</v>
+      </c>
+      <c r="I5" s="12">
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1664,28 +1667,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-21.95</v>
+        <v>-16.95</v>
       </c>
       <c r="F6" s="19">
-        <v>-26.15</v>
+        <v>-22.15</v>
       </c>
       <c r="G6" s="19">
         <v>2.58</v>
       </c>
       <c r="H6" s="19">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="8">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1693,19 +1696,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
+        <v>-22.15</v>
+      </c>
+      <c r="F7" s="22">
         <v>-26.15</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-30.15</v>
       </c>
       <c r="G7" s="22">
         <v>0.83</v>
@@ -1722,28 +1725,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-30.15</v>
+        <v>-26.15</v>
       </c>
       <c r="F8" s="25">
-        <v>-36.47</v>
+        <v>-30.5</v>
       </c>
       <c r="G8" s="25">
         <v>1.5</v>
       </c>
       <c r="H8" s="25">
-        <v>6.32</v>
+        <v>4.35</v>
       </c>
       <c r="I8" s="8">
-        <v>4.21</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1751,16 +1754,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-36.47</v>
+        <v>-30.5</v>
       </c>
       <c r="F9" s="28">
         <v>-44.25</v>
@@ -1769,27 +1772,27 @@
         <v>2.58</v>
       </c>
       <c r="H9" s="28">
-        <v>7.78</v>
-      </c>
-      <c r="I9" s="8">
-        <v>3.01</v>
+        <v>13.75</v>
+      </c>
+      <c r="I9" s="12">
+        <v>5.32</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-3.73</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.25</v>

--- a/SGC-CKN/Excel/3cfb93bc-b746-45bb-98e2-62340827647b_PA-159_PA-159_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/3cfb93bc-b746-45bb-98e2-62340827647b_PA-159_PA-159_D800_25-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>01:45 25/03/2026</t>
+    <t>01:15 25/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -178,7 +178,7 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">01:45
+    <t xml:space="preserve">01:15
 25/03/2026</t>
   </si>
   <si>
@@ -1151,16 +1151,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.73</v>
+        <v>-1.75</v>
       </c>
       <c r="H11" s="5">
         <v>0.42</v>
       </c>
       <c r="I11" s="5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J11" s="8">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1183,7 +1183,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.73</v>
+        <v>-1.75</v>
       </c>
       <c r="G12" s="9">
         <v>-4.85</v>
@@ -1192,10 +1192,10 @@
         <v>0.58</v>
       </c>
       <c r="I12" s="9">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="J12" s="12">
-        <v>5.35</v>
+        <v>5.31</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1361,16 +1361,16 @@
         <v>-26.15</v>
       </c>
       <c r="G17" s="25">
-        <v>-30.5</v>
+        <v>-36.47</v>
       </c>
       <c r="H17" s="25">
         <v>1.5</v>
       </c>
       <c r="I17" s="25">
-        <v>4.35</v>
-      </c>
-      <c r="J17" s="8">
-        <v>2.9</v>
+        <v>10.32</v>
+      </c>
+      <c r="J17" s="12">
+        <v>6.88</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
@@ -1393,19 +1393,19 @@
         <v>52</v>
       </c>
       <c r="F18" s="28">
-        <v>-30.5</v>
+        <v>-36.47</v>
       </c>
       <c r="G18" s="28">
-        <v>-44.25</v>
+        <v>-44.23</v>
       </c>
       <c r="H18" s="28">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="I18" s="28">
-        <v>13.75</v>
-      </c>
-      <c r="J18" s="12">
-        <v>5.32</v>
+        <v>7.76</v>
+      </c>
+      <c r="J18" s="8">
+        <v>3.72</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1563,16 +1563,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.73</v>
+        <v>-1.75</v>
       </c>
       <c r="G2" s="5">
         <v>0.42</v>
       </c>
       <c r="H2" s="5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I2" s="8">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1589,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.73</v>
+        <v>-1.75</v>
       </c>
       <c r="F3" s="9">
         <v>-4.85</v>
@@ -1598,10 +1598,10 @@
         <v>0.58</v>
       </c>
       <c r="H3" s="9">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="I3" s="12">
-        <v>5.35</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1737,16 +1737,16 @@
         <v>-26.15</v>
       </c>
       <c r="F8" s="25">
-        <v>-30.5</v>
+        <v>-36.47</v>
       </c>
       <c r="G8" s="25">
         <v>1.5</v>
       </c>
       <c r="H8" s="25">
-        <v>4.35</v>
-      </c>
-      <c r="I8" s="8">
-        <v>2.9</v>
+        <v>10.32</v>
+      </c>
+      <c r="I8" s="12">
+        <v>6.88</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,19 +1763,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-30.5</v>
+        <v>-36.47</v>
       </c>
       <c r="F9" s="28">
-        <v>-44.25</v>
+        <v>-44.23</v>
       </c>
       <c r="G9" s="28">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="H9" s="28">
-        <v>13.75</v>
-      </c>
-      <c r="I9" s="12">
-        <v>5.32</v>
+        <v>7.76</v>
+      </c>
+      <c r="I9" s="8">
+        <v>3.72</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1795,16 +1795,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="33">
-        <v>-44.25</v>
+        <v>-44.23</v>
       </c>
       <c r="G10" s="33">
-        <v>10.42</v>
+        <v>9.92</v>
       </c>
       <c r="H10" s="33">
-        <v>44.25</v>
+        <v>44.23</v>
       </c>
       <c r="I10" s="33">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>
